--- a/artfynd/A 787-2023 artfynd.xlsx
+++ b/artfynd/A 787-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 787-2023 artfynd.xlsx
+++ b/artfynd/A 787-2023 artfynd.xlsx
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76689292</v>
+        <v>76689293</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>350m N om Västby, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757679.175891404</v>
+        <v>757679</v>
       </c>
       <c r="R2" t="n">
-        <v>7159576.134521971</v>
+        <v>7159576</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,14 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fåtal plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>källa</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,55 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76689293</v>
+        <v>76689292</v>
       </c>
       <c r="B3" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1256</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>350m N om Västby, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757679.175891404</v>
+        <v>757679</v>
       </c>
       <c r="R3" t="n">
-        <v>7159576.134521971</v>
+        <v>7159576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +855,9 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>fåtal plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,11 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>källa</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 787-2023 artfynd.xlsx
+++ b/artfynd/A 787-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76689293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76689292</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>